--- a/Month-1/Day-8/Hungerstation Logistics & Delivery Fleet Dashboard.xlsx
+++ b/Month-1/Day-8/Hungerstation Logistics & Delivery Fleet Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data-Analysis-and-AI-85Days\Month-1\Day-8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{10219B2E-D570-4068-BA95-273EA1F23CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089BFF4D-B0FF-46B9-80E9-C20E37233F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{88D4364E-7EF7-4403-A28E-AC9F1EAAC678}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="56">
   <si>
     <t>ahmed_Al-Otaibi</t>
   </si>
@@ -305,7 +305,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -497,11 +497,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -563,8 +576,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -592,6 +603,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1300,23 +1314,107 @@
           </c:errBars>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$15:$K$16</c:f>
+              <c:f>Sheet1!$K$15:$K$30</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>Abha</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Dammam</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Hail</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Jeddah</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Jizan</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jubail</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Khobar</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Makkah</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Medina</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Najran</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>Qassim</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Riyadh</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Tabuk</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Taif</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Yanbu</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$L$15:$L$16</c:f>
+              <c:f>Sheet1!$L$15:$L$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1434,22 +1532,106 @@
           </c:errBars>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$15:$K$16</c:f>
+              <c:f>Sheet1!$K$15:$K$30</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>Abha</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Dammam</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Hail</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Jeddah</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Jizan</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jubail</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Khobar</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Makkah</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Medina</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Najran</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>Qassim</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Riyadh</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Tabuk</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Taif</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Yanbu</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$M$15:$M$16</c:f>
+              <c:f>Sheet1!$M$15:$M$30</c:f>
               <c:numCache>
                 <c:formatCode>[$⃁-401]\ #,##0.00</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>35</c:v>
                 </c:pt>
               </c:numCache>
@@ -1568,23 +1750,107 @@
           </c:errBars>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$15:$K$16</c:f>
+              <c:f>Sheet1!$K$15:$K$30</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>Abha</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Dammam</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Hail</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Jeddah</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Jizan</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Jubail</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Khobar</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Makkah</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Medina</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Najran</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>Qassim</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Riyadh</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Tabuk</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Taif</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Yanbu</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$N$15:$N$16</c:f>
+              <c:f>Sheet1!$N$15:$N$30</c:f>
               <c:numCache>
                 <c:formatCode>[$⃁-401]\ #,##0.00</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>645</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>225</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>315</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>255</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1230</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>180</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2445,7 +2711,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>402980</xdr:colOff>
+      <xdr:colOff>402979</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>109904</xdr:rowOff>
     </xdr:to>
@@ -2483,8 +2749,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="14801505" y="2818825"/>
-              <a:ext cx="2914563" cy="3043432"/>
+              <a:off x="15157872" y="2817815"/>
+              <a:ext cx="2922134" cy="3075738"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -2791,32 +3057,32 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3147ACA9-1307-4349-8E24-EFF2EDC22A43}" name="PivotTable3" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
-  <location ref="K14:N16" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <location ref="K14:N30" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="22">
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
-        <item h="1" x="2"/>
-        <item h="1" x="3"/>
-        <item h="1" x="4"/>
-        <item h="1" x="5"/>
-        <item h="1" x="6"/>
-        <item h="1" x="7"/>
-        <item h="1" x="8"/>
-        <item h="1" x="9"/>
-        <item h="1" x="10"/>
-        <item h="1" x="11"/>
-        <item h="1" x="12"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
         <item x="13"/>
-        <item h="1" x="14"/>
-        <item h="1" x="15"/>
-        <item h="1" x="16"/>
-        <item h="1" x="17"/>
-        <item h="1" x="18"/>
-        <item h="1" m="1" x="20"/>
-        <item h="1" x="19"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item m="1" x="20"/>
+        <item x="19"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2847,9 +3113,51 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="2">
+  <rowItems count="16">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
     <i>
       <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
     </i>
     <i t="grand">
       <x/>
@@ -2932,27 +3240,27 @@
   <data>
     <tabular pivotCacheId="647512839">
       <items count="21">
-        <i x="0"/>
-        <i x="1"/>
-        <i x="2"/>
-        <i x="3"/>
-        <i x="4"/>
-        <i x="5"/>
-        <i x="6"/>
-        <i x="7"/>
-        <i x="8"/>
-        <i x="9"/>
-        <i x="10"/>
-        <i x="11"/>
-        <i x="12"/>
+        <i x="0" s="1"/>
+        <i x="1" s="1"/>
+        <i x="2" s="1"/>
+        <i x="3" s="1"/>
+        <i x="4" s="1"/>
+        <i x="5" s="1"/>
+        <i x="6" s="1"/>
+        <i x="7" s="1"/>
+        <i x="8" s="1"/>
+        <i x="9" s="1"/>
+        <i x="10" s="1"/>
+        <i x="11" s="1"/>
+        <i x="12" s="1"/>
         <i x="13" s="1"/>
-        <i x="14"/>
-        <i x="15"/>
-        <i x="16"/>
-        <i x="17"/>
-        <i x="18"/>
-        <i x="19"/>
-        <i x="20" nd="1"/>
+        <i x="14" s="1"/>
+        <i x="15" s="1"/>
+        <i x="16" s="1"/>
+        <i x="17" s="1"/>
+        <i x="18" s="1"/>
+        <i x="19" s="1"/>
+        <i x="20" s="1" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -3314,7 +3622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9C4DE04-05D7-4D54-A5D1-300078CB69CC}">
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:R30"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="21.54296875" bestFit="1" customWidth="1"/>
@@ -3324,13 +3632,13 @@
     <col min="5" max="5" width="17.90625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.7265625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.36328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="15" t="s">
         <v>41</v>
       </c>
@@ -3343,7 +3651,7 @@
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
     </row>
-    <row r="2" spans="1:17" ht="14.5" customHeight="1">
+    <row r="2" spans="1:18" ht="14.5" customHeight="1">
       <c r="A2" s="15"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -3362,7 +3670,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="21"/>
     </row>
-    <row r="3" spans="1:17" ht="14.5" customHeight="1">
+    <row r="3" spans="1:18" ht="14.5" customHeight="1">
       <c r="A3" s="15"/>
       <c r="B3" s="5" t="s">
         <v>34</v>
@@ -3383,15 +3691,15 @@
         <v>39</v>
       </c>
       <c r="J3" s="17"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="26"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="24"/>
     </row>
-    <row r="4" spans="1:17" ht="18.5">
+    <row r="4" spans="1:18" ht="18.5">
       <c r="A4" s="15"/>
       <c r="B4" s="3">
         <v>106</v>
@@ -3412,19 +3720,19 @@
         <v>30</v>
       </c>
       <c r="J4" s="18"/>
-      <c r="K4" s="28">
+      <c r="K4" s="26">
         <v>307</v>
       </c>
-      <c r="L4" s="28"/>
-      <c r="M4" s="29" t="s">
+      <c r="L4" s="26"/>
+      <c r="M4" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
     </row>
-    <row r="5" spans="1:17" ht="18.5">
+    <row r="5" spans="1:18" ht="18.5">
       <c r="A5" s="15"/>
       <c r="B5" s="3">
         <v>101</v>
@@ -3445,19 +3753,19 @@
         <v>45</v>
       </c>
       <c r="J5" s="18"/>
-      <c r="K5" s="30">
+      <c r="K5" s="28">
         <v>4605</v>
       </c>
-      <c r="L5" s="30"/>
-      <c r="M5" s="29" t="s">
+      <c r="L5" s="28"/>
+      <c r="M5" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
     </row>
-    <row r="6" spans="1:17" ht="18.5">
+    <row r="6" spans="1:18" ht="18.5">
       <c r="A6" s="15"/>
       <c r="B6" s="3">
         <v>117</v>
@@ -3478,19 +3786,19 @@
         <v>60</v>
       </c>
       <c r="J6" s="18"/>
-      <c r="K6" s="30">
+      <c r="K6" s="28">
         <v>890</v>
       </c>
-      <c r="L6" s="30"/>
-      <c r="M6" s="29" t="s">
+      <c r="L6" s="28"/>
+      <c r="M6" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
     </row>
-    <row r="7" spans="1:17" ht="18.5">
+    <row r="7" spans="1:18" ht="18.5">
       <c r="A7" s="15"/>
       <c r="B7" s="3">
         <v>113</v>
@@ -3511,19 +3819,19 @@
         <v>30</v>
       </c>
       <c r="J7" s="18"/>
-      <c r="K7" s="31">
+      <c r="K7" s="29">
         <v>15.35</v>
       </c>
-      <c r="L7" s="31"/>
-      <c r="M7" s="29" t="s">
+      <c r="L7" s="29"/>
+      <c r="M7" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27"/>
     </row>
-    <row r="8" spans="1:17" ht="18.5">
+    <row r="8" spans="1:18" ht="18.5">
       <c r="A8" s="15"/>
       <c r="B8" s="3">
         <v>114</v>
@@ -3544,19 +3852,19 @@
         <v>45</v>
       </c>
       <c r="J8" s="18"/>
-      <c r="K8" s="28">
+      <c r="K8" s="26">
         <v>44.5</v>
       </c>
-      <c r="L8" s="28"/>
-      <c r="M8" s="29" t="s">
+      <c r="L8" s="26"/>
+      <c r="M8" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
+      <c r="Q8" s="27"/>
     </row>
-    <row r="9" spans="1:17" ht="18.5">
+    <row r="9" spans="1:18" ht="18.5">
       <c r="A9" s="15"/>
       <c r="B9" s="3">
         <v>104</v>
@@ -3577,19 +3885,19 @@
         <v>60</v>
       </c>
       <c r="J9" s="18"/>
-      <c r="K9" s="28">
+      <c r="K9" s="34">
         <v>20</v>
       </c>
-      <c r="L9" s="28"/>
-      <c r="M9" s="29" t="s">
+      <c r="L9" s="26"/>
+      <c r="M9" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29"/>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="27"/>
+      <c r="P9" s="27"/>
+      <c r="Q9" s="27"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10" s="15"/>
       <c r="B10" s="3">
         <v>102</v>
@@ -3609,15 +3917,17 @@
       <c r="G10" s="4">
         <v>50</v>
       </c>
-      <c r="K10" s="23"/>
-      <c r="L10" s="24"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="22"/>
       <c r="M10" s="22"/>
       <c r="N10" s="22"/>
       <c r="O10" s="22"/>
       <c r="P10" s="22"/>
-      <c r="Q10" s="24"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="16"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11" s="15"/>
       <c r="B11" s="3">
         <v>120</v>
@@ -3645,7 +3955,7 @@
       <c r="P11" s="16"/>
       <c r="Q11" s="16"/>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12" s="15"/>
       <c r="B12" s="3">
         <v>107</v>
@@ -3670,7 +3980,7 @@
       <c r="M12" s="16"/>
       <c r="N12" s="16"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13" s="15"/>
       <c r="B13" s="3">
         <v>103</v>
@@ -3695,7 +4005,7 @@
       <c r="M13" s="16"/>
       <c r="N13" s="16"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14" s="15"/>
       <c r="B14" s="3">
         <v>118</v>
@@ -3715,7 +4025,7 @@
       <c r="G14" s="4">
         <v>35</v>
       </c>
-      <c r="K14" s="33" t="s">
+      <c r="K14" s="31" t="s">
         <v>50</v>
       </c>
       <c r="L14" t="s">
@@ -3728,7 +4038,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15" s="15"/>
       <c r="B15" s="3">
         <v>111</v>
@@ -3748,20 +4058,20 @@
       <c r="G15" s="4">
         <v>40</v>
       </c>
-      <c r="K15" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="L15" s="35">
-        <v>11</v>
-      </c>
-      <c r="M15" s="32">
-        <v>35</v>
-      </c>
-      <c r="N15" s="32">
-        <v>165</v>
+      <c r="K15" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" s="33">
+        <v>13</v>
+      </c>
+      <c r="M15" s="30">
+        <v>40</v>
+      </c>
+      <c r="N15" s="30">
+        <v>195</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16" s="15"/>
       <c r="B16" s="3">
         <v>115</v>
@@ -3781,20 +4091,20 @@
       <c r="G16" s="4">
         <v>25</v>
       </c>
-      <c r="K16" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="L16" s="35">
-        <v>11</v>
-      </c>
-      <c r="M16" s="32">
+      <c r="K16" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="L16" s="33">
+        <v>12</v>
+      </c>
+      <c r="M16" s="30">
         <v>35</v>
       </c>
-      <c r="N16" s="32">
-        <v>165</v>
+      <c r="N16" s="30">
+        <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:14">
       <c r="A17" s="15"/>
       <c r="B17" s="3">
         <v>109</v>
@@ -3814,8 +4124,20 @@
       <c r="G17" s="4">
         <v>35</v>
       </c>
+      <c r="K17" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17" s="33">
+        <v>8</v>
+      </c>
+      <c r="M17" s="30">
+        <v>25</v>
+      </c>
+      <c r="N17" s="30">
+        <v>120</v>
+      </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:14">
       <c r="A18" s="15"/>
       <c r="B18" s="3">
         <v>116</v>
@@ -3835,8 +4157,20 @@
       <c r="G18" s="4">
         <v>40</v>
       </c>
+      <c r="K18" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="33">
+        <v>43</v>
+      </c>
+      <c r="M18" s="30">
+        <v>125</v>
+      </c>
+      <c r="N18" s="30">
+        <v>645</v>
+      </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:14">
       <c r="A19" s="15"/>
       <c r="B19" s="3">
         <v>108</v>
@@ -3856,8 +4190,20 @@
       <c r="G19" s="4">
         <v>55</v>
       </c>
+      <c r="K19" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="33">
+        <v>15</v>
+      </c>
+      <c r="M19" s="30">
+        <v>45</v>
+      </c>
+      <c r="N19" s="30">
+        <v>225</v>
+      </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:14">
       <c r="A20" s="15"/>
       <c r="B20" s="3">
         <v>105</v>
@@ -3877,8 +4223,20 @@
       <c r="G20" s="4">
         <v>40</v>
       </c>
+      <c r="K20" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="L20" s="33">
+        <v>21</v>
+      </c>
+      <c r="M20" s="30">
+        <v>60</v>
+      </c>
+      <c r="N20" s="30">
+        <v>315</v>
+      </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:14">
       <c r="A21" s="15"/>
       <c r="B21" s="3">
         <v>110</v>
@@ -3898,8 +4256,20 @@
       <c r="G21" s="4">
         <v>50</v>
       </c>
+      <c r="K21" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="33">
+        <v>17</v>
+      </c>
+      <c r="M21" s="30">
+        <v>50</v>
+      </c>
+      <c r="N21" s="30">
+        <v>255</v>
+      </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:14">
       <c r="A22" s="15"/>
       <c r="B22" s="3">
         <v>119</v>
@@ -3919,8 +4289,20 @@
       <c r="G22" s="4">
         <v>45</v>
       </c>
+      <c r="K22" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="33">
+        <v>14</v>
+      </c>
+      <c r="M22" s="30">
+        <v>40</v>
+      </c>
+      <c r="N22" s="30">
+        <v>210</v>
+      </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:14">
       <c r="A23" s="15"/>
       <c r="B23" s="8">
         <v>112</v>
@@ -3940,8 +4322,20 @@
       <c r="G23" s="11">
         <v>55</v>
       </c>
+      <c r="K23" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="L23" s="33">
+        <v>16</v>
+      </c>
+      <c r="M23" s="30">
+        <v>45</v>
+      </c>
+      <c r="N23" s="30">
+        <v>240</v>
+      </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:14">
       <c r="B24" s="8" t="s">
         <v>49</v>
       </c>
@@ -3965,11 +4359,105 @@
         <f>SUM(G4:G23)</f>
         <v>890</v>
       </c>
+      <c r="K24" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L24" s="33">
+        <v>14</v>
+      </c>
+      <c r="M24" s="30">
+        <v>40</v>
+      </c>
+      <c r="N24" s="30">
+        <v>210</v>
+      </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="25" spans="1:14">
+      <c r="K25" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="L25" s="33">
+        <v>11</v>
+      </c>
+      <c r="M25" s="30">
+        <v>35</v>
+      </c>
+      <c r="N25" s="30">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="K26" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="L26" s="33">
+        <v>82</v>
+      </c>
+      <c r="M26" s="30">
+        <v>230</v>
+      </c>
+      <c r="N26" s="30">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="K27" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="L27" s="33">
+        <v>19</v>
+      </c>
+      <c r="M27" s="30">
+        <v>55</v>
+      </c>
+      <c r="N27" s="30">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="14"/>
       <c r="B28" s="14"/>
       <c r="C28" s="14"/>
+      <c r="K28" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="L28" s="33">
+        <v>10</v>
+      </c>
+      <c r="M28" s="30">
+        <v>30</v>
+      </c>
+      <c r="N28" s="30">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="K29" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29" s="33">
+        <v>12</v>
+      </c>
+      <c r="M29" s="30">
+        <v>35</v>
+      </c>
+      <c r="N29" s="30">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="K30" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="L30" s="33">
+        <v>307</v>
+      </c>
+      <c r="M30" s="30">
+        <v>890</v>
+      </c>
+      <c r="N30" s="30">
+        <v>4605</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="16">
